--- a/home_inspection_forms/004_schedule_a_free_inspection--home_inspection_forms.xlsx
+++ b/home_inspection_forms/004_schedule_a_free_inspection--home_inspection_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -1122,8 +1122,8 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="26" customWidth="1" min="1" max="1"/>
-    <col width="36" customWidth="1" min="2" max="2"/>
-    <col width="36" customWidth="1" min="3" max="3"/>
+    <col width="15" customWidth="1" min="2" max="2"/>
+    <col width="15" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1151,12 +1151,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>{'id':_1,_'name':_'email'}</t>
+          <t>email</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>{'id': 1, 'name': 'Email'}</t>
+          <t>Email</t>
         </is>
       </c>
     </row>
@@ -1168,12 +1168,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>{'id':_2,_'name':_'phone'}</t>
+          <t>phone</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>{'id': 2, 'name': 'Phone'}</t>
+          <t>Phone</t>
         </is>
       </c>
     </row>
@@ -1185,12 +1185,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>{'id':_3,_'name':_'other'}</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>{'id': 3, 'name': 'Other'}</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
@@ -1202,12 +1202,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>{'id':_1,_'name':_'single_family'}</t>
+          <t>single_family</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>{'id': 1, 'name': 'Single Family'}</t>
+          <t>Single Family</t>
         </is>
       </c>
     </row>
@@ -1219,12 +1219,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>{'id':_2,_'name':_'townhouse'}</t>
+          <t>townhouse</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>{'id': 2, 'name': 'Townhouse'}</t>
+          <t>Townhouse</t>
         </is>
       </c>
     </row>
@@ -1236,12 +1236,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>{'id':_3,_'name':_'condo'}</t>
+          <t>condo</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>{'id': 3, 'name': 'Condo'}</t>
+          <t>Condo</t>
         </is>
       </c>
     </row>
@@ -1253,12 +1253,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>{'id':_4,_'name':_'other'}</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>{'id': 4, 'name': 'Other'}</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
@@ -1270,12 +1270,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>{'id':_1,_'name':_'email'}</t>
+          <t>email</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>{'id': 1, 'name': 'Email'}</t>
+          <t>Email</t>
         </is>
       </c>
     </row>
@@ -1287,12 +1287,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>{'id':_2,_'name':_'phone'}</t>
+          <t>phone</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>{'id': 2, 'name': 'Phone'}</t>
+          <t>Phone</t>
         </is>
       </c>
     </row>
@@ -1304,12 +1304,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>{'id':_3,_'name':_'other'}</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>{'id': 3, 'name': 'Other'}</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
@@ -1321,12 +1321,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>{'id':_1,_'name':_'email'}</t>
+          <t>email</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>{'id': 1, 'name': 'Email'}</t>
+          <t>Email</t>
         </is>
       </c>
     </row>
@@ -1338,12 +1338,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>{'id':_2,_'name':_'phone'}</t>
+          <t>phone</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>{'id': 2, 'name': 'Phone'}</t>
+          <t>Phone</t>
         </is>
       </c>
     </row>
@@ -1355,12 +1355,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>{'id':_3,_'name':_'other'}</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>{'id': 3, 'name': 'Other'}</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
@@ -1372,12 +1372,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>{'id':_1,_'name':_'active'}</t>
+          <t>active</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>{'id': 1, 'name': 'Active'}</t>
+          <t>Active</t>
         </is>
       </c>
     </row>
@@ -1389,12 +1389,12 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>{'id':_2,_'name':_'inactive'}</t>
+          <t>inactive</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>{'id': 2, 'name': 'Inactive'}</t>
+          <t>Inactive</t>
         </is>
       </c>
     </row>
@@ -1406,12 +1406,12 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>{'id':_3,_'name':_'sold'}</t>
+          <t>sold</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>{'id': 3, 'name': 'Sold'}</t>
+          <t>Sold</t>
         </is>
       </c>
     </row>
